--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -2903,7 +2903,7 @@
         <v>113110136</v>
       </c>
       <c r="B18" t="n">
-        <v>90243</v>
+        <v>90259</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -2903,7 +2903,7 @@
         <v>113110136</v>
       </c>
       <c r="B18" t="n">
-        <v>90259</v>
+        <v>90271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>101201</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418681.7318415901</v>
+        <v>418682</v>
       </c>
       <c r="R2" t="n">
-        <v>6505423.5425952</v>
+        <v>6505424</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1989-08-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103521</v>
+        <v>103532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103532</v>
+        <v>103540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103540</v>
+        <v>103552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103552</v>
+        <v>103560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103560</v>
+        <v>103562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103562</v>
+        <v>103589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103589</v>
+        <v>103602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103602</v>
+        <v>103606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>705191</v>
       </c>
       <c r="B2" t="n">
-        <v>103606</v>
+        <v>103613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28254-2023 artfynd.xlsx
+++ b/artfynd/A 28254-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110133</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110164</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110134</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110169</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110135</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110157</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110168</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2355255</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2355256</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113110165</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2002,6 +2062,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98533017</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2144,6 +2209,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98533018</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2281,6 +2351,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98532908</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2423,6 +2498,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98532909</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2560,6 +2640,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98532910</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2702,6 +2787,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98533001</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2844,6 +2934,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98533002</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2981,6 +3076,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98533003</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3118,6 +3218,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98532858</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3260,6 +3365,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98532859</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3402,6 +3512,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98532860</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3539,6 +3654,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98532861</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3681,6 +3801,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98533058</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3818,6 +3943,11 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98533059</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3960,8 +4090,41 @@
           <t>Fladdermöss i skyddade områden-Västra Götalands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98532812</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>